--- a/artfynd/A 15202-2023 artfynd.xlsx
+++ b/artfynd/A 15202-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15202-2023 artfynd.xlsx
+++ b/artfynd/A 15202-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108178324</v>
+        <v>108179619</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876462.7030705881</v>
+        <v>876508</v>
       </c>
       <c r="R2" t="n">
-        <v>7358578.852390415</v>
+        <v>7358431</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,14 +756,14 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108176346</v>
+        <v>108176348</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876442.4283279076</v>
+        <v>876463</v>
       </c>
       <c r="R3" t="n">
-        <v>7358433.55863992</v>
+        <v>7358514</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,31 +879,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108180981</v>
+        <v>108176412</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -938,17 +923,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lapintarha, Nb</t>
+          <t>Husaoja, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876491.8294173958</v>
+        <v>876445</v>
       </c>
       <c r="R4" t="n">
-        <v>7358328.341955782</v>
+        <v>7358519</v>
       </c>
       <c r="S4" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +999,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108176348</v>
+        <v>108180776</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1055,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876463.6404146871</v>
+        <v>876516</v>
       </c>
       <c r="R5" t="n">
-        <v>7358513.838685944</v>
+        <v>7358342</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,67 +1095,58 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108174272</v>
+        <v>108180929</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Husaoja, Nb</t>
+          <t>Lapintarha, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876442.4283279076</v>
+        <v>876462</v>
       </c>
       <c r="R6" t="n">
-        <v>7358433.55863992</v>
+        <v>7358319</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,14 +1188,14 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1232,66 +1203,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108179619</v>
+        <v>108180981</v>
       </c>
       <c r="B7" t="n">
-        <v>90472</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Husaoja, Nb</t>
+          <t>Lapintarha, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876508</v>
+        <v>876492</v>
       </c>
       <c r="R7" t="n">
-        <v>7358431</v>
+        <v>7358329</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,27 +1311,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108179003</v>
+        <v>108174272</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,24 +1334,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876462.7030705881</v>
+        <v>876443</v>
       </c>
       <c r="R8" t="n">
-        <v>7358578.852390415</v>
+        <v>7358434</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1433,7 +1398,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,14 +1408,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1470,15 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108180776</v>
+        <v>108178324</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876515.9152216744</v>
+        <v>876462</v>
       </c>
       <c r="R9" t="n">
-        <v>7358341.409347212</v>
+        <v>7358578</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,7 +1506,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,14 +1516,14 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1583,19 +1543,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108176975</v>
+        <v>108176346</v>
       </c>
       <c r="B10" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1624,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876428.4745251448</v>
+        <v>876443</v>
       </c>
       <c r="R10" t="n">
-        <v>7358589.414429464</v>
+        <v>7358434</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,49 +1639,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108179362</v>
+        <v>108176975</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876508.4574831058</v>
+        <v>876429</v>
       </c>
       <c r="R11" t="n">
-        <v>7358430.543483692</v>
+        <v>7358589</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,49 +1747,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108176412</v>
+        <v>108179003</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876445.3441225083</v>
+        <v>876462</v>
       </c>
       <c r="R12" t="n">
-        <v>7358518.756343066</v>
+        <v>7358578</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,131 +1855,15 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>108180785</v>
-      </c>
-      <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Husaoja, Nb</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>876470.5058066433</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7358355.797473589</v>
-      </c>
-      <c r="S13" t="n">
-        <v>25</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Övertorneå</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Hietaniemi</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Viktoria Sturk</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Viktoria Sturk</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15202-2023 artfynd.xlsx
+++ b/artfynd/A 15202-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108179619</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108176348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108176412</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108180776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108180929</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108180981</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108174272</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108178324</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108176346</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108176975</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,8 +1919,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108179003</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>